--- a/users.xlsx
+++ b/users.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\سيستم تحويل الفواتير\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C095F824-6DF5-4AC2-AECE-3AC11F937023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{712DD2BA-B218-46D5-B199-3595A04742B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{C9D13CF7-8CFE-4F60-9C0C-A019D2C8D598}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
   <si>
     <t>Username</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>User</t>
+  </si>
+  <si>
+    <t>hussein</t>
   </si>
 </sst>
 </file>
@@ -428,11 +431,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9BDE0BC-D126-4FC1-984A-2E6EBAA6DBA9}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.83984375" style="1"/>
-    <col min="2" max="2" width="11.68359375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.20703125" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.83984375" style="1"/>
   </cols>
   <sheetData>
@@ -502,6 +505,17 @@
         <v>9</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1119885757</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
